--- a/exports/TMPV_full_report.xlsx
+++ b/exports/TMPV_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.19</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>347.6</v>
+        <v>332.55</v>
       </c>
       <c r="I2" t="n">
         <v>344.1481493245051</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0.19</v>
+        <v>-4.15</v>
       </c>
       <c r="L2" t="n">
-        <v>2.48</v>
+        <v>5.09</v>
       </c>
       <c r="M2" t="n">
         <v>1.17</v>
       </c>
       <c r="N2" t="n">
-        <v>2.58</v>
+        <v>5.39</v>
       </c>
       <c r="O2" t="n">
         <v>2.82</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>9.08</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44592.38541666666</v>
+        <v>44592.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>349.8</v>
+        <v>356.55</v>
       </c>
       <c r="I3" t="n">
         <v>353.3358350262972</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.19</v>
+        <v>-7.22</v>
       </c>
       <c r="L3" t="n">
-        <v>5.44</v>
+        <v>7.65</v>
       </c>
       <c r="M3" t="n">
         <v>1.58</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>332.15</v>
+        <v>324.3</v>
       </c>
       <c r="I4" t="n">
         <v>330.1778748499889</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.84</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>8.08</v>
+        <v>9.48</v>
       </c>
       <c r="M4" t="n">
         <v>2.15</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.87</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>291.9</v>
+        <v>298.3</v>
       </c>
       <c r="I5" t="n">
         <v>296.1055436535923</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>9.99</v>
+        <v>8.02</v>
       </c>
       <c r="L5" t="n">
         <v>8.56</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>312</v>
+        <v>300.2</v>
       </c>
       <c r="I6" t="n">
         <v>301.2538436558034</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>4.59</v>
+        <v>0.64</v>
       </c>
       <c r="L6" t="n">
         <v>2.77</v>
@@ -783,7 +854,7 @@
         <v>1.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1.47</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>2.38</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.85</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44693.55208333334</v>
+        <v>44694.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>256.05</v>
+        <v>284.4</v>
       </c>
       <c r="I7" t="n">
         <v>280.3943625588786</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>14.71</v>
+        <v>5.26</v>
       </c>
       <c r="L7" t="n">
         <v>3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>2.45</v>
+        <v>4.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.83</v>
+        <v>8.59</v>
       </c>
       <c r="O7" t="n">
         <v>-3.32</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.87</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>294.25</v>
+        <v>281.65</v>
       </c>
       <c r="I8" t="n">
         <v>286.2236437990457</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>3.46</v>
+        <v>-0.97</v>
       </c>
       <c r="L8" t="n">
         <v>6.31</v>
@@ -897,7 +992,7 @@
         <v>3.96</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>4.88</v>
       </c>
       <c r="O8" t="n">
         <v>8.59</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>6.92</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>281.4</v>
+        <v>286.65</v>
       </c>
       <c r="I9" t="n">
         <v>282.6129485624167</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09</v>
+        <v>-1.78</v>
       </c>
       <c r="L9" t="n">
         <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="N9" t="n">
         <v>3.64</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>324.95</v>
+        <v>316.8</v>
       </c>
       <c r="I10" t="n">
         <v>320.7011882243095</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>13.36</v>
+        <v>10.52</v>
       </c>
       <c r="L10" t="n">
         <v>3.37</v>
@@ -1011,7 +1130,7 @@
         <v>1.36</v>
       </c>
       <c r="N10" t="n">
-        <v>2.67</v>
+        <v>3.91</v>
       </c>
       <c r="O10" t="n">
         <v>1.05</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>285.05</v>
+        <v>290.05</v>
       </c>
       <c r="I11" t="n">
         <v>285.6480843956521</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>71</v>
+        <v>71.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>10.02</v>
+        <v>8.44</v>
       </c>
       <c r="L11" t="n">
         <v>3.09</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.88</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>298.2</v>
+        <v>284.3</v>
       </c>
       <c r="I12" t="n">
         <v>287.2869800364694</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K12" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="L12" t="n">
         <v>2.81</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.78</v>
-      </c>
       <c r="M12" t="n">
-        <v>0.76</v>
+        <v>2.92</v>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>4.59</v>
       </c>
       <c r="O12" t="n">
         <v>2.18</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44879.55208333334</v>
+        <v>44880.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>298.45</v>
+        <v>300.8</v>
       </c>
       <c r="I13" t="n">
         <v>299.7083915534138</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.98</v>
+        <v>-5.8</v>
       </c>
       <c r="L13" t="n">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M13" t="n">
         <v>1.63</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.35</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44901.55208333334</v>
+        <v>44902.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>293.9</v>
+        <v>290.2</v>
       </c>
       <c r="I14" t="n">
         <v>292.8454985999132</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.29</v>
+        <v>-3.52</v>
       </c>
       <c r="L14" t="n">
         <v>3.96</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>4.31</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44935.55208333334</v>
+        <v>44936.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>267.75</v>
+        <v>284.7</v>
       </c>
       <c r="I15" t="n">
         <v>275.2072079312895</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>7.74</v>
+        <v>1.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>1.35</v>
+        <v>2.86</v>
       </c>
       <c r="N15" t="n">
-        <v>2.54</v>
+        <v>6.07</v>
       </c>
       <c r="O15" t="n">
         <v>-1.63</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>294.25</v>
+        <v>285.05</v>
       </c>
       <c r="I16" t="n">
         <v>292.3273740715376</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>0.12</v>
       </c>
       <c r="L16" t="n">
         <v>3.27</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>294.55</v>
+        <v>300.85</v>
       </c>
       <c r="I17" t="n">
         <v>300.3738502025495</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.33</v>
+        <v>-5.54</v>
       </c>
       <c r="L17" t="n">
-        <v>3.98</v>
+        <v>5.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="N17" t="n">
-        <v>1.67</v>
+        <v>3.09</v>
       </c>
       <c r="O17" t="n">
         <v>-1.97</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.96</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>291.7</v>
+        <v>286.15</v>
       </c>
       <c r="I18" t="n">
         <v>290.1967043197108</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.04</v>
+        <v>-4.89</v>
       </c>
       <c r="L18" t="n">
-        <v>4.06</v>
+        <v>5.35</v>
       </c>
       <c r="M18" t="n">
         <v>0.46</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.64</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>287.85</v>
+        <v>289.8</v>
       </c>
       <c r="I19" t="n">
         <v>289.5618964266533</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.59</v>
+        <v>-1.28</v>
       </c>
       <c r="L19" t="n">
         <v>2.06</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.55</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45140.38541666666</v>
+        <v>45140.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>430.35</v>
+        <v>428.95</v>
       </c>
       <c r="I20" t="n">
         <v>428.9927863967318</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>123.8333333333333</v>
+        <v>124</v>
       </c>
       <c r="K20" t="n">
-        <v>48.5</v>
+        <v>48.02</v>
       </c>
       <c r="L20" t="n">
         <v>0.74</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>166</v>
+        <v>167</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.39</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45177.38541666666</v>
+        <v>45177.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>430.15</v>
+        <v>431.65</v>
       </c>
       <c r="I21" t="n">
         <v>430.8857013528221</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.28</v>
+        <v>-0.63</v>
       </c>
       <c r="L21" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>0.86</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.53</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45194.38541666666</v>
+        <v>45194.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>428.9</v>
+        <v>426.2</v>
       </c>
       <c r="I22" t="n">
         <v>426.491605099939</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.64</v>
+        <v>-1.26</v>
       </c>
       <c r="L22" t="n">
         <v>1.86</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.04</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>433.95</v>
+        <v>437.7</v>
       </c>
       <c r="I23" t="n">
         <v>437.3803420109857</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.82</v>
+        <v>-2.7</v>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="M23" t="n">
         <v>1.23</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.51</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>445.1</v>
+        <v>438.45</v>
       </c>
       <c r="I24" t="n">
         <v>441.4929493165143</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>1.69</v>
+        <v>0.17</v>
       </c>
       <c r="L24" t="n">
         <v>0.49</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.3</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>450</v>
+        <v>457.15</v>
       </c>
       <c r="I25" t="n">
         <v>452.7945192018875</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.63</v>
+        <v>-4.27</v>
       </c>
       <c r="L25" t="n">
         <v>4.58</v>
@@ -1866,7 +2165,7 @@
         <v>3.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="O25" t="n">
         <v>-1.33</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.68</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>499.8</v>
+        <v>486.1</v>
       </c>
       <c r="I26" t="n">
         <v>487.8300425969908</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>9.33</v>
+        <v>6.33</v>
       </c>
       <c r="L26" t="n">
         <v>1.12</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>4.88</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45286.55208333334</v>
+        <v>45287.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>495.95</v>
+        <v>505.9</v>
       </c>
       <c r="I27" t="n">
         <v>503.9625308969029</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.03</v>
+        <v>-4.07</v>
       </c>
       <c r="L27" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>2.13</v>
+        <v>2.77</v>
       </c>
       <c r="O27" t="n">
         <v>-3.28</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.63</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>685.8</v>
+        <v>670.3</v>
       </c>
       <c r="I28" t="n">
         <v>674.5049202153073</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>77</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>35.56</v>
+        <v>32.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.31</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.09</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45385.38541666666</v>
+        <v>45385.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>690</v>
+        <v>695.4</v>
       </c>
       <c r="I29" t="n">
         <v>694.4501087628311</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.94</v>
+        <v>-3.74</v>
       </c>
       <c r="L29" t="n">
-        <v>3.73</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
         <v>0.73</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>687.1</v>
+        <v>678.15</v>
       </c>
       <c r="I30" t="n">
         <v>679.0058507636652</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.19</v>
+        <v>-2.48</v>
       </c>
       <c r="L30" t="n">
         <v>3.12</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.39</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45411.55208333334</v>
+        <v>45412.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>688.55</v>
+        <v>698</v>
       </c>
       <c r="I31" t="n">
         <v>694.7933010278764</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.53</v>
+        <v>-2.93</v>
       </c>
       <c r="L31" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
         <v>1.48</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.89</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>699.8</v>
+        <v>681.9</v>
       </c>
       <c r="I32" t="n">
         <v>682.3345813379168</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>0.26</v>
+        <v>-2.31</v>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="N32" t="n">
-        <v>1.49</v>
+        <v>2.79</v>
       </c>
       <c r="O32" t="n">
         <v>0.89</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>6.08</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45422.38541666666</v>
+        <v>45422.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>712.2</v>
+        <v>720.85</v>
       </c>
       <c r="I33" t="n">
         <v>712.8295780591961</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.44</v>
+        <v>-5.71</v>
       </c>
       <c r="L33" t="n">
-        <v>5.81</v>
+        <v>6.05</v>
       </c>
       <c r="M33" t="n">
         <v>0.59</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>5.62</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45422.55208333334</v>
+        <v>45425.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>720.85</v>
+        <v>661.3</v>
       </c>
       <c r="I34" t="n">
         <v>680.3377816066427</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>-8.26</v>
       </c>
       <c r="L34" t="n">
-        <v>1.24</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>4.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O34" t="n">
         <v>1.56</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45450.38541666666</v>
+        <v>45450.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>661.5</v>
+        <v>667.85</v>
       </c>
       <c r="I35" t="n">
         <v>667.1321532988356</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03</v>
+        <v>-0.99</v>
       </c>
       <c r="L35" t="n">
         <v>5.02</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.08</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>753.9</v>
+        <v>707.1</v>
       </c>
       <c r="I36" t="n">
         <v>753.303477602004</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>56</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>12.88</v>
+        <v>5.88</v>
       </c>
       <c r="L36" t="n">
         <v>2.26</v>
       </c>
       <c r="M36" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>4.14</v>
+        <v>7.28</v>
       </c>
       <c r="O36" t="n">
         <v>3.25</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45533.38541666666</v>
+        <v>45533.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>737.05</v>
+        <v>765.7</v>
       </c>
       <c r="I37" t="n">
         <v>757.1961818863131</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.24</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>7.79</v>
+        <v>11.19</v>
       </c>
       <c r="M37" t="n">
         <v>1.72</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.01</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>735.8</v>
+        <v>720.65</v>
       </c>
       <c r="I38" t="n">
         <v>722.35522406833</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.9</v>
+        <v>-5.88</v>
       </c>
       <c r="L38" t="n">
-        <v>4.06</v>
+        <v>6.03</v>
       </c>
       <c r="M38" t="n">
         <v>0.7</v>
       </c>
       <c r="N38" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="O38" t="n">
         <v>3.57</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.07</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>516.25</v>
+        <v>521</v>
       </c>
       <c r="I39" t="n">
         <v>520.4843022688483</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>117.1666666666667</v>
+        <v>118</v>
       </c>
       <c r="K39" t="n">
-        <v>28.36</v>
+        <v>27.7</v>
       </c>
       <c r="L39" t="n">
         <v>2.51</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>4.52</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45670.38541666666</v>
+        <v>45670.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>523.6</v>
+        <v>517</v>
       </c>
       <c r="I40" t="n">
         <v>517.2265853465482</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5</v>
+        <v>-0.77</v>
       </c>
       <c r="L40" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="M40" t="n">
         <v>0.96</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45727.55208333334</v>
+        <v>45728.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>446.75</v>
+        <v>457.95</v>
       </c>
       <c r="I41" t="n">
         <v>449.9327760059087</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>13.59</v>
+        <v>11.42</v>
       </c>
       <c r="L41" t="n">
         <v>4.76</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>5.91</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45742.55208333334</v>
+        <v>45743.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>487.05</v>
+        <v>460.8</v>
       </c>
       <c r="I42" t="n">
         <v>471.1399283543259</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K42" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="L42" t="n">
         <v>2.34</v>
       </c>
       <c r="M42" t="n">
-        <v>0.02</v>
+        <v>5.57</v>
       </c>
       <c r="N42" t="n">
-        <v>2.01</v>
+        <v>5.36</v>
       </c>
       <c r="O42" t="n">
         <v>2.97</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.98</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>410.6</v>
+        <v>428.5</v>
       </c>
       <c r="I43" t="n">
         <v>423.5540783832378</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>10.89</v>
+        <v>7.01</v>
       </c>
       <c r="L43" t="n">
         <v>2.34</v>
@@ -2892,7 +3407,7 @@
         <v>4.31</v>
       </c>
       <c r="N43" t="n">
-        <v>1.97</v>
+        <v>4.38</v>
       </c>
       <c r="O43" t="n">
         <v>-5.36</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>491.9</v>
+        <v>486</v>
       </c>
       <c r="I44" t="n">
         <v>489.1283460806035</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K44" t="n">
-        <v>14.8</v>
+        <v>13.42</v>
       </c>
       <c r="L44" t="n">
         <v>2.26</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.36</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>475.5</v>
+        <v>482.1</v>
       </c>
       <c r="I45" t="n">
         <v>479.2468241133761</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>2.16</v>
+        <v>0.8</v>
       </c>
       <c r="L45" t="n">
         <v>1.29</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.98</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45867.55208333334</v>
+        <v>45868.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>476.25</v>
+        <v>460.9</v>
       </c>
       <c r="I46" t="n">
         <v>464.3104356321808</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.21</v>
+        <v>-4.4</v>
       </c>
       <c r="L46" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
         <v>0.31</v>
       </c>
       <c r="N46" t="n">
-        <v>1.92</v>
+        <v>3.43</v>
       </c>
       <c r="O46" t="n">
         <v>1.5</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>6</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>456.55</v>
+        <v>466.7</v>
       </c>
       <c r="I47" t="n">
         <v>458.6924730443347</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="L47" t="n">
         <v>3.07</v>
       </c>
       <c r="M47" t="n">
-        <v>0.88</v>
+        <v>2.09</v>
       </c>
       <c r="N47" t="n">
         <v>3.71</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>4.52</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>483.45</v>
+        <v>473.05</v>
       </c>
       <c r="I48" t="n">
         <v>478.4192925777151</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K48" t="n">
-        <v>3.59</v>
+        <v>1.36</v>
       </c>
       <c r="L48" t="n">
         <v>1.48</v>
       </c>
       <c r="M48" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="N48" t="n">
-        <v>1.69</v>
+        <v>2.68</v>
       </c>
       <c r="O48" t="n">
         <v>1.93</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.14</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>469.45</v>
+        <v>490.4</v>
       </c>
       <c r="I49" t="n">
         <v>480.0138568211642</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>0.76</v>
+        <v>-3.67</v>
       </c>
       <c r="L49" t="n">
-        <v>2.36</v>
+        <v>3.76</v>
       </c>
       <c r="M49" t="n">
         <v>1.59</v>
       </c>
       <c r="N49" t="n">
-        <v>1.27</v>
+        <v>5.27</v>
       </c>
       <c r="O49" t="n">
         <v>-2.68</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.71</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45938.38541666666</v>
+        <v>45938.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>474.15</v>
+        <v>468.2</v>
       </c>
       <c r="I50" t="n">
         <v>472.3770353767936</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.31</v>
+        <v>-4.53</v>
       </c>
       <c r="L50" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="M50" t="n">
         <v>0.36</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.06</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>354.55</v>
+        <v>358.65</v>
       </c>
       <c r="I51" t="n">
         <v>356.2001265413572</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>72</v>
+        <v>74.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>24.27</v>
+        <v>23.4</v>
       </c>
       <c r="L51" t="n">
         <v>19.96</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.5</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>363</v>
+        <v>360.05</v>
       </c>
       <c r="I52" t="n">
         <v>360.6301896190581</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K52" t="n">
-        <v>1.21</v>
+        <v>0.39</v>
       </c>
       <c r="L52" t="n">
         <v>1.41</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>343.2</v>
+        <v>359.3</v>
       </c>
       <c r="I53" t="n">
         <v>356.7079266155253</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>4.68</v>
+        <v>0.21</v>
       </c>
       <c r="L53" t="n">
         <v>1.47</v>
@@ -3462,7 +4097,7 @@
         <v>1.55</v>
       </c>
       <c r="N53" t="n">
-        <v>3.34</v>
+        <v>6.06</v>
       </c>
       <c r="O53" t="n">
         <v>-1.2</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9.58</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>383.5</v>
+        <v>369.85</v>
       </c>
       <c r="I54" t="n">
         <v>370.68442391456</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>6.74</v>
+        <v>2.94</v>
       </c>
       <c r="L54" t="n">
         <v>5.07</v>
       </c>
       <c r="M54" t="n">
-        <v>2.82</v>
+        <v>6.65</v>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>3.21</v>
       </c>
       <c r="O54" t="n">
         <v>6.06</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.39</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>308.75</v>
+        <v>334.05</v>
       </c>
       <c r="I55" t="n">
         <v>319.2270896450448</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>16.52</v>
+        <v>9.68</v>
       </c>
       <c r="L55" t="n">
         <v>2.31</v>
@@ -3576,7 +4235,7 @@
         <v>4.22</v>
       </c>
       <c r="N55" t="n">
-        <v>3.67</v>
+        <v>8.76</v>
       </c>
       <c r="O55" t="n">
         <v>-3.21</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.58</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>352.45</v>
+        <v>337.85</v>
       </c>
       <c r="I56" t="n">
         <v>342.4099305472968</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K56" t="n">
-        <v>5.51</v>
+        <v>1.14</v>
       </c>
       <c r="L56" t="n">
         <v>4.52</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>358.25</v>
+        <v>360.75</v>
       </c>
       <c r="I57" t="n">
         <v>360.4818223420386</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.04</v>
+        <v>-6.78</v>
       </c>
       <c r="L57" t="n">
-        <v>6.25</v>
+        <v>6.99</v>
       </c>
       <c r="M57" t="n">
         <v>1.39</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.14</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>345.7</v>
+        <v>338.5</v>
       </c>
       <c r="I58" t="n">
         <v>340.5099863613885</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.17</v>
+        <v>-6.17</v>
       </c>
       <c r="L58" t="n">
-        <v>4.31</v>
+        <v>6.25</v>
       </c>
       <c r="M58" t="n">
         <v>0.9</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.47</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>338.25</v>
+        <v>362.45</v>
       </c>
       <c r="I59" t="n">
         <v>355.2392918881173</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>0.07000000000000001</v>
+        <v>-7.08</v>
       </c>
       <c r="L59" t="n">
-        <v>2.13</v>
+        <v>8.4</v>
       </c>
       <c r="M59" t="n">
-        <v>0.92</v>
+        <v>4.07</v>
       </c>
       <c r="N59" t="n">
-        <v>0.39</v>
+        <v>5.37</v>
       </c>
       <c r="O59" t="n">
         <v>-2.24</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>7.51</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46183.55208333334</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>381</v>
+        <v>375.15</v>
       </c>
       <c r="I60" t="n">
         <v>378.258414267416</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K60" t="n">
-        <v>5.12</v>
+        <v>3.5</v>
       </c>
       <c r="L60" t="n">
         <v>3.13</v>
       </c>
       <c r="M60" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="N60" t="n">
         <v>2.47</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>5.67</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>391</v>
+        <v>398.15</v>
       </c>
       <c r="I61" t="n">
         <v>396.2357684451014</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.22</v>
+        <v>-6.13</v>
       </c>
       <c r="L61" t="n">
-        <v>4.74</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>1.05</v>
+        <v>1.84</v>
       </c>
       <c r="N61" t="n">
         <v>3.91</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.38</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>382.4</v>
+        <v>361.65</v>
       </c>
       <c r="I62" t="n">
         <v>376.7189748035212</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.96</v>
+        <v>-9.17</v>
       </c>
       <c r="L62" t="n">
-        <v>4.07</v>
+        <v>10.84</v>
       </c>
       <c r="M62" t="n">
         <v>-0</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>11.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46233.38541666666</v>
+        <v>46233.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>332.5</v>
+        <v>335</v>
       </c>
       <c r="I63" t="n">
         <v>334.846159177457</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K63" t="n">
-        <v>8.06</v>
+        <v>7.37</v>
       </c>
       <c r="L63" t="n">
         <v>6.36</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.11</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>347.25</v>
+        <v>335.75</v>
       </c>
       <c r="I64" t="n">
         <v>336.2592506764721</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>3.66</v>
+        <v>0.22</v>
       </c>
       <c r="L64" t="n">
         <v>1.04</v>
@@ -4089,7 +4856,7 @@
         <v>0.23</v>
       </c>
       <c r="N64" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="O64" t="n">
         <v>1.72</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.86</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46282.38541666666</v>
+        <v>46282.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>306.05</v>
+        <v>315</v>
       </c>
       <c r="I65" t="n">
         <v>312.4458374530593</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>8.85</v>
+        <v>6.18</v>
       </c>
       <c r="L65" t="n">
         <v>4.71</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.77</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46289.55208333334</v>
+        <v>46290.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>295.55</v>
+        <v>288.9</v>
       </c>
       <c r="I66" t="n">
         <v>293.6785255232978</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.17</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>6.35</v>
+        <v>8.35</v>
       </c>
       <c r="M66" t="n">
         <v>1.71</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>42</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7176,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123.8</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7206,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7236,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7256,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7266,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.06</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.45</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.67</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7296,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48.5</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7306,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7316,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.62</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7326,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -6535,7 +7346,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7356,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7366,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="25">
@@ -6575,7 +7386,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7396,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.18</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7406,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
